--- a/output/excel/joint_gap_metrics_joint_gap_c6_u30_k3_s4_seed43.xlsx
+++ b/output/excel/joint_gap_metrics_joint_gap_c6_u30_k3_s4_seed43.xlsx
@@ -544,7 +544,7 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>27.0180726</v>
+        <v>39.7446693</v>
       </c>
       <c r="M2">
         <v>26620</v>
@@ -588,7 +588,7 @@
         <v>0.02677990520920227</v>
       </c>
       <c r="L3">
-        <v>4.587470400000001</v>
+        <v>7.7125792</v>
       </c>
       <c r="M3">
         <v>10</v>
@@ -656,7 +656,7 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>5.889536115589976</v>
+        <v>5.153226731208154</v>
       </c>
       <c r="F2">
         <v>317.8938126967806</v>
